--- a/education_forms/013_ai_education_research_partnership_request_form--education_forms.xlsx
+++ b/education_forms/013_ai_education_research_partnership_request_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -988,8 +988,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'academic-industry_collaboration',_'value':_'academic_industry'}</t>
+          <t>academic-industry_collaboration</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Academic-Industry Collaboration', 'value': 'academic_industry'}</t>
+          <t>Academic-Industry Collaboration</t>
         </is>
       </c>
     </row>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'inter-university_partnership',_'value':_'inter_university'}</t>
+          <t>inter-university_partnership</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Inter-University Partnership', 'value': 'inter_university'}</t>
+          <t>Inter-University Partnership</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'non-profit_/_public_sector_collaboration',_'value':_'non_profit_public'}</t>
+          <t>non-profit_/_public_sector_collaboration</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Non-Profit / Public Sector Collaboration', 'value': 'non_profit_public'}</t>
+          <t>Non-Profit / Public Sector Collaboration</t>
         </is>
       </c>
     </row>
@@ -1068,12 +1068,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'technology_provider_partnership',_'value':_'tech_provider'}</t>
+          <t>technology_provider_partnership</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Technology Provider Partnership', 'value': 'tech_provider'}</t>
+          <t>Technology Provider Partnership</t>
         </is>
       </c>
     </row>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'generative_ai_/_llms_in_the_classroom',_'value':_'gen_ai'}</t>
+          <t>generative_ai_/_llms_in_the_classroom</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Generative AI / LLMs in the Classroom', 'value': 'gen_ai'}</t>
+          <t>Generative AI / LLMs in the Classroom</t>
         </is>
       </c>
     </row>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'personalized_/_adaptive_learning_systems',_'value':_'personalized_learning'}</t>
+          <t>personalized_/_adaptive_learning_systems</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Personalized / Adaptive Learning Systems', 'value': 'personalized_learning'}</t>
+          <t>Personalized / Adaptive Learning Systems</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1119,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'ai_ethics_and_policy_in_education',_'value':_'ethics_policy'}</t>
+          <t>ai_ethics_and_policy_in_education</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'AI Ethics and Policy in Education', 'value': 'ethics_policy'}</t>
+          <t>AI Ethics and Policy in Education</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1136,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'intelligent_tutoring_systems',_'value':_'tutoring_systems'}</t>
+          <t>intelligent_tutoring_systems</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Intelligent Tutoring Systems', 'value': 'tutoring_systems'}</t>
+          <t>Intelligent Tutoring Systems</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1153,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'automated_assessment_&amp;_feedback',_'value':_'assessment'}</t>
+          <t>automated_assessment_&amp;_feedback</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Automated Assessment &amp; Feedback', 'value': 'assessment'}</t>
+          <t>Automated Assessment &amp; Feedback</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'educational_data_mining_/_analytics',_'value':_'data_mining'}</t>
+          <t>educational_data_mining_/_analytics</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Educational Data Mining / Analytics', 'value': 'data_mining'}</t>
+          <t>Educational Data Mining / Analytics</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'early_childhood_(pre-k)',_'value':_'early_childhood'}</t>
+          <t>early_childhood_(pre-k)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Early Childhood (Pre-K)', 'value': 'early_childhood'}</t>
+          <t>Early Childhood (Pre-K)</t>
         </is>
       </c>
     </row>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'k-12_education',_'value':_'k12'}</t>
+          <t>k-12_education</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'K-12 Education', 'value': 'k12'}</t>
+          <t>K-12 Education</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'higher_education_(undergraduate/graduate)',_'value':_'higher_ed'}</t>
+          <t>higher_education_(undergraduate/graduate)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Higher Education (Undergraduate/Graduate)', 'value': 'higher_ed'}</t>
+          <t>Higher Education (Undergraduate/Graduate)</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'vocational_/_professional_training',_'value':_'vocational'}</t>
+          <t>vocational_/_professional_training</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Vocational / Professional Training', 'value': 'vocational'}</t>
+          <t>Vocational / Professional Training</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'informal_/_lifelong_learning',_'value':_'informal'}</t>
+          <t>informal_/_lifelong_learning</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Informal / Lifelong Learning', 'value': 'informal'}</t>
+          <t>Informal / Lifelong Learning</t>
         </is>
       </c>
     </row>
@@ -1272,12 +1272,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'fully_funded',_'value':_'fully_funded'}</t>
+          <t>fully_funded</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Fully Funded', 'value': 'fully_funded'}</t>
+          <t>Fully Funded</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'partially_funded',_'value':_'partially_funded'}</t>
+          <t>partially_funded</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Partially Funded', 'value': 'partially_funded'}</t>
+          <t>Partially Funded</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'seeking_funding_(grant_proposal_phase)',_'value':_'seeking'}</t>
+          <t>seeking_funding_(grant_proposal_phase)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Seeking Funding (Grant Proposal Phase)', 'value': 'seeking'}</t>
+          <t>Seeking Funding (Grant Proposal Phase)</t>
         </is>
       </c>
     </row>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'not_funded_(in-kind_partnership_only)',_'value':_'not_funded'}</t>
+          <t>not_funded_(in-kind_partnership_only)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Not Funded (In-kind partnership only)', 'value': 'not_funded'}</t>
+          <t>Not Funded (In-kind partnership only)</t>
         </is>
       </c>
     </row>
@@ -1340,12 +1340,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'approved',_'value':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Approved', 'value': 'approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'submitted_/_pending',_'value':_'pending'}</t>
+          <t>submitted_/_pending</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Submitted / Pending', 'value': 'pending'}</t>
+          <t>Submitted / Pending</t>
         </is>
       </c>
     </row>
@@ -1374,12 +1374,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'not_yet_submitted',_'value':_'not_submitted'}</t>
+          <t>not_yet_submitted</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Not Yet Submitted', 'value': 'not_submitted'}</t>
+          <t>Not Yet Submitted</t>
         </is>
       </c>
     </row>
@@ -1391,12 +1391,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable',_'value':_'na'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Not Applicable', 'value': 'na'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
